--- a/data/trans_orig/P57B3_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P57B3_2023-Edad-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según se ha sentido solo/a en 2023</t>
+          <t>Población según se ha sentido solo/a en 2023 (tasa de respuesta: 99,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>163</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10040</t>
+          <t>11560</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>315</t>
+          <t>321</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>16706</t>
+          <t>16533</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1893</t>
+          <t>2190</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>19304</t>
+          <t>18876</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,65%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1275</t>
+          <t>1266</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18218</t>
+          <t>21830</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9880</t>
+          <t>10054</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>33696</t>
+          <t>35179</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>13839</t>
+          <t>13103</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>45758</t>
+          <t>42988</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,03%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>108090</t>
+          <t>110731</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>175328</t>
+          <t>178895</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>27,02%</t>
+          <t>27,68%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>43,83%</t>
+          <t>44,73%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>62312</t>
+          <t>63137</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>100968</t>
+          <t>104605</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>19,9%</t>
+          <t>20,16%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>32,24%</t>
+          <t>33,4%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>184193</t>
+          <t>180830</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>261088</t>
+          <t>262527</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>25,83%</t>
+          <t>25,36%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>36,61%</t>
+          <t>36,81%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>215774</t>
+          <t>214444</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>282231</t>
+          <t>281808</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>53,95%</t>
+          <t>53,61%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>70,56%</t>
+          <t>70,45%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>187759</t>
+          <t>187514</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>230932</t>
+          <t>229770</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>59,95%</t>
+          <t>59,87%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>73,73%</t>
+          <t>73,36%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>419946</t>
+          <t>415612</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>497300</t>
+          <t>499619</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>58,88%</t>
+          <t>58,28%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>69,73%</t>
+          <t>70,05%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2538</t>
+          <t>2241</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>14440</t>
+          <t>14394</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4850</t>
+          <t>4308</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>19778</t>
+          <t>18729</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>9327</t>
+          <t>9691</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>29107</t>
+          <t>28956</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,1%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>12720</t>
+          <t>13388</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>35282</t>
+          <t>36283</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>16061</t>
+          <t>15652</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>39778</t>
+          <t>39652</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>32110</t>
+          <t>33511</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>64898</t>
+          <t>64956</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,95%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>114353</t>
+          <t>112343</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>162129</t>
+          <t>160034</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>27,0%</t>
+          <t>26,52%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>38,28%</t>
+          <t>37,78%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>70661</t>
+          <t>75971</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>149705</t>
+          <t>148478</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>29,27%</t>
+          <t>29,03%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>193365</t>
+          <t>198874</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>295179</t>
+          <t>295458</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>20,68%</t>
+          <t>21,27%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>31,57%</t>
+          <t>31,6%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>231292</t>
+          <t>232378</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>283141</t>
+          <t>284204</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>54,61%</t>
+          <t>54,86%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>66,85%</t>
+          <t>67,1%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>318160</t>
+          <t>320481</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>417672</t>
+          <t>410015</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>62,2%</t>
+          <t>62,65%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>81,66%</t>
+          <t>80,16%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>567070</t>
+          <t>569802</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>694350</t>
+          <t>688283</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>60,65%</t>
+          <t>60,94%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>74,26%</t>
+          <t>73,61%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>8665</t>
+          <t>8770</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>24116</t>
+          <t>24956</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>6982</t>
+          <t>7310</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>18057</t>
+          <t>18372</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>18819</t>
+          <t>18588</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>37748</t>
+          <t>37485</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,48%</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>31198</t>
+          <t>30863</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>56324</t>
+          <t>57279</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1996,12 +1996,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2016,12 +2016,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>19699</t>
+          <t>19101</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>36359</t>
+          <t>35974</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2051,12 +2051,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>56592</t>
+          <t>55230</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>87427</t>
+          <t>86308</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,02%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>131375</t>
+          <t>130786</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>176454</t>
+          <t>172985</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>24,54%</t>
+          <t>24,43%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>32,96%</t>
+          <t>32,31%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>151479</t>
+          <t>151498</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>186669</t>
+          <t>186930</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2149,7 +2149,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>34,52%</t>
+          <t>34,57%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>293209</t>
+          <t>293326</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>346609</t>
+          <t>348839</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>27,25%</t>
+          <t>27,26%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>32,21%</t>
+          <t>32,42%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>301185</t>
+          <t>301557</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>347550</t>
+          <t>349408</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>56,26%</t>
+          <t>56,33%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>64,92%</t>
+          <t>65,27%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>314577</t>
+          <t>316000</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>352376</t>
+          <t>352944</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>58,17%</t>
+          <t>58,43%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>65,16%</t>
+          <t>65,26%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>629774</t>
+          <t>625648</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>688192</t>
+          <t>686096</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>58,52%</t>
+          <t>58,14%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>63,95%</t>
+          <t>63,76%</t>
         </is>
       </c>
     </row>
@@ -2437,12 +2437,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>36757</t>
+          <t>37842</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>604434</t>
+          <t>629533</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2452,12 +2452,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>68,08%</t>
+          <t>70,91%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>14629</t>
+          <t>14147</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>28878</t>
+          <t>28748</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>55687</t>
+          <t>56239</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>830242</t>
+          <t>883349</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>51,9%</t>
+          <t>55,22%</t>
         </is>
       </c>
     </row>
@@ -2550,12 +2550,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>18605</t>
+          <t>19007</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>69372</t>
+          <t>69308</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>31168</t>
+          <t>30306</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>51853</t>
+          <t>51743</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2600,12 +2600,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2620,12 +2620,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>48331</t>
+          <t>49469</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>107955</t>
+          <t>109997</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,88%</t>
         </is>
       </c>
     </row>
@@ -2663,12 +2663,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>88909</t>
+          <t>79302</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>281459</t>
+          <t>282664</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>31,7%</t>
+          <t>31,84%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2698,12 +2698,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>200354</t>
+          <t>203222</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>259973</t>
+          <t>259740</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>28,15%</t>
+          <t>28,55%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>36,52%</t>
+          <t>36,49%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>238190</t>
+          <t>246035</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>519773</t>
+          <t>523880</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>32,49%</t>
+          <t>32,75%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>171231</t>
+          <t>162136</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>527497</t>
+          <t>528013</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>18,26%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>59,42%</t>
+          <t>59,48%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>389188</t>
+          <t>388502</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>457272</t>
+          <t>456925</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>54,68%</t>
+          <t>54,58%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>64,24%</t>
+          <t>64,19%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>474248</t>
+          <t>434968</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>944096</t>
+          <t>944860</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>29,65%</t>
+          <t>27,19%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>59,02%</t>
+          <t>59,07%</t>
         </is>
       </c>
     </row>
@@ -3006,12 +3006,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>24741</t>
+          <t>24801</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>46250</t>
+          <t>45899</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3021,12 +3021,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3041,12 +3041,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>17991</t>
+          <t>18535</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>33127</t>
+          <t>33833</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3076,12 +3076,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>46755</t>
+          <t>47698</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>72839</t>
+          <t>72715</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,56%</t>
         </is>
       </c>
     </row>
@@ -3119,12 +3119,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>47055</t>
+          <t>47464</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>73453</t>
+          <t>73707</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3154,12 +3154,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>46217</t>
+          <t>47019</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>67038</t>
+          <t>67974</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3189,12 +3189,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>98626</t>
+          <t>100194</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>133501</t>
+          <t>133136</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>12,02%</t>
         </is>
       </c>
     </row>
@@ -3232,12 +3232,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>159786</t>
+          <t>160614</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>201361</t>
+          <t>202702</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3247,12 +3247,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>28,47%</t>
+          <t>28,62%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>35,88%</t>
+          <t>36,12%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3267,12 +3267,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>193391</t>
+          <t>192957</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>227679</t>
+          <t>227078</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>35,37%</t>
+          <t>35,3%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>41,65%</t>
+          <t>41,54%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3302,12 +3302,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>363223</t>
+          <t>362112</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>416363</t>
+          <t>417899</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>32,78%</t>
+          <t>32,68%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>37,58%</t>
+          <t>37,72%</t>
         </is>
       </c>
     </row>
@@ -3345,12 +3345,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>261766</t>
+          <t>265558</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>309170</t>
+          <t>311619</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3360,12 +3360,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>46,64%</t>
+          <t>47,32%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>55,09%</t>
+          <t>55,52%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>235758</t>
+          <t>237729</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>270772</t>
+          <t>272902</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3395,12 +3395,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>43,12%</t>
+          <t>43,48%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>49,53%</t>
+          <t>49,92%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>513302</t>
+          <t>517610</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>572109</t>
+          <t>573632</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3430,12 +3430,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>46,33%</t>
+          <t>46,72%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>51,64%</t>
+          <t>51,78%</t>
         </is>
       </c>
     </row>
@@ -3575,12 +3575,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>8834</t>
+          <t>8803</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>21438</t>
+          <t>19907</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3590,12 +3590,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>8584</t>
+          <t>8279</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>35857</t>
+          <t>35582</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3645,12 +3645,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>17029</t>
+          <t>18546</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>49686</t>
+          <t>50410</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,16%</t>
         </is>
       </c>
     </row>
@@ -3688,12 +3688,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>23934</t>
+          <t>24473</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>40404</t>
+          <t>41043</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3703,12 +3703,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>21418</t>
+          <t>26248</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>91166</t>
+          <t>91814</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3738,12 +3738,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3758,12 +3758,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>47311</t>
+          <t>47168</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>118997</t>
+          <t>119622</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3773,12 +3773,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>12,25%</t>
         </is>
       </c>
     </row>
@@ -3801,12 +3801,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>115099</t>
+          <t>115403</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>146403</t>
+          <t>145639</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>31,26%</t>
+          <t>31,35%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>39,77%</t>
+          <t>39,56%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3836,12 +3836,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>64759</t>
+          <t>68761</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>238973</t>
+          <t>239337</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3851,12 +3851,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>39,28%</t>
+          <t>39,34%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3871,12 +3871,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>159166</t>
+          <t>148778</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>368050</t>
+          <t>368950</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3886,12 +3886,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>37,69%</t>
+          <t>37,78%</t>
         </is>
       </c>
     </row>
@@ -3914,12 +3914,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>176048</t>
+          <t>176393</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>207452</t>
+          <t>207389</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3929,12 +3929,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>47,82%</t>
+          <t>47,91%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>56,35%</t>
+          <t>56,33%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3949,12 +3949,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>249590</t>
+          <t>249968</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>511438</t>
+          <t>501938</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3964,12 +3964,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>41,03%</t>
+          <t>41,09%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>84,07%</t>
+          <t>82,51%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3984,12 +3984,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>449547</t>
+          <t>446895</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>750976</t>
+          <t>759689</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3999,12 +3999,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>46,04%</t>
+          <t>45,76%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>76,9%</t>
+          <t>77,79%</t>
         </is>
       </c>
     </row>
@@ -4144,12 +4144,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>15373</t>
+          <t>15241</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>29523</t>
+          <t>28518</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4159,12 +4159,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>36336</t>
+          <t>35243</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>53635</t>
+          <t>53522</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>54659</t>
+          <t>55650</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>77448</t>
+          <t>78071</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>11,06%</t>
         </is>
       </c>
     </row>
@@ -4257,12 +4257,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>23762</t>
+          <t>24461</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>40364</t>
+          <t>40058</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4272,12 +4272,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4292,12 +4292,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>64825</t>
+          <t>64293</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>86321</t>
+          <t>85801</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4307,12 +4307,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>20,36%</t>
+          <t>20,24%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4327,12 +4327,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>93458</t>
+          <t>92565</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>120322</t>
+          <t>120033</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,11%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>17,01%</t>
         </is>
       </c>
     </row>
@@ -4370,12 +4370,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>89283</t>
+          <t>89620</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>113103</t>
+          <t>114574</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4385,12 +4385,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>31,67%</t>
+          <t>31,79%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>40,12%</t>
+          <t>40,64%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4405,12 +4405,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>148598</t>
+          <t>148354</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>178369</t>
+          <t>175132</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4420,12 +4420,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>35,05%</t>
+          <t>34,99%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>42,07%</t>
+          <t>41,31%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4440,12 +4440,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>244676</t>
+          <t>245396</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>283592</t>
+          <t>282640</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>34,66%</t>
+          <t>34,77%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>40,18%</t>
+          <t>40,04%</t>
         </is>
       </c>
     </row>
@@ -4483,12 +4483,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>113805</t>
+          <t>114661</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>140568</t>
+          <t>140405</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4498,12 +4498,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>40,37%</t>
+          <t>40,68%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>49,87%</t>
+          <t>49,81%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4518,12 +4518,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>129715</t>
+          <t>130976</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>158045</t>
+          <t>158353</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4533,12 +4533,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>30,6%</t>
+          <t>30,89%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>37,28%</t>
+          <t>37,35%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4553,12 +4553,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>250838</t>
+          <t>251494</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>288668</t>
+          <t>290465</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4568,12 +4568,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>35,54%</t>
+          <t>35,63%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>40,9%</t>
+          <t>41,15%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>127244</t>
+          <t>126748</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>1040145</t>
+          <t>1119406</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>30,08%</t>
+          <t>32,37%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>114171</t>
+          <t>112890</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>160826</t>
+          <t>159945</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>261836</t>
+          <t>263767</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>1454463</t>
+          <t>1372465</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>20,44%</t>
+          <t>19,29%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>184248</t>
+          <t>184640</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>275812</t>
+          <t>273593</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>249101</t>
+          <t>245828</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>334553</t>
+          <t>337159</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>469975</t>
+          <t>470160</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>595762</t>
+          <t>592055</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4916,7 +4916,7 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,32%</t>
         </is>
       </c>
     </row>
@@ -4939,12 +4939,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>823630</t>
+          <t>818316</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>1137197</t>
+          <t>1133051</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4954,12 +4954,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>23,82%</t>
+          <t>23,66%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>32,89%</t>
+          <t>32,77%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4974,12 +4974,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>933543</t>
+          <t>939586</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>1224976</t>
+          <t>1225748</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4989,12 +4989,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>25,7%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>33,5%</t>
+          <t>33,52%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5009,12 +5009,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>1884033</t>
+          <t>1867144</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>2313594</t>
+          <t>2325161</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5024,12 +5024,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>26,48%</t>
+          <t>26,25%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>32,52%</t>
+          <t>32,68%</t>
         </is>
       </c>
     </row>
@@ -5052,12 +5052,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>1401663</t>
+          <t>1350780</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>1976983</t>
+          <t>1979854</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5067,12 +5067,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>40,53%</t>
+          <t>39,06%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>57,17%</t>
+          <t>57,26%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5087,12 +5087,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>1958955</t>
+          <t>1959813</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>2380505</t>
+          <t>2344653</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5102,12 +5102,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>53,58%</t>
+          <t>53,6%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>65,11%</t>
+          <t>64,13%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5122,12 +5122,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>3463186</t>
+          <t>3482742</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>4153567</t>
+          <t>4132562</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5137,12 +5137,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>48,68%</t>
+          <t>48,95%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>58,38%</t>
+          <t>58,09%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P57B3_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P57B3_2023-Edad-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>3170</t>
+          <t>5078</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>1331</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11560</t>
+          <t>14204</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>4295</t>
+          <t>5538</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>321</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>16533</t>
+          <t>17410</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>7465</t>
+          <t>10616</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2190</t>
+          <t>4197</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>18876</t>
+          <t>23540</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>3,06%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6206</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1266</t>
+          <t>1334</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>21830</t>
+          <t>19975</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>19277</t>
+          <t>22954</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10054</t>
+          <t>12733</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>35179</t>
+          <t>39183</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>25483</t>
+          <t>29193</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>13103</t>
+          <t>16717</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>42988</t>
+          <t>48634</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,31%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>139657</t>
+          <t>146661</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>110731</t>
+          <t>116043</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>178895</t>
+          <t>177411</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>34,92%</t>
+          <t>35,96%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>27,68%</t>
+          <t>28,46%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>44,73%</t>
+          <t>43,51%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,22 +986,22 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>80461</t>
+          <t>95147</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>63137</t>
+          <t>73070</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>104605</t>
+          <t>119151</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>25,69%</t>
+          <t>26,25%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>33,4%</t>
+          <t>32,87%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>220118</t>
+          <t>241808</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>180830</t>
+          <t>206129</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>262527</t>
+          <t>287020</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>30,86%</t>
+          <t>31,39%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>25,36%</t>
+          <t>26,76%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>36,81%</t>
+          <t>37,26%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>250953</t>
+          <t>249815</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>214444</t>
+          <t>218906</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>281808</t>
+          <t>279587</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>62,74%</t>
+          <t>61,26%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>53,61%</t>
+          <t>53,68%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>70,45%</t>
+          <t>68,56%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>209167</t>
+          <t>238872</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>187514</t>
+          <t>215705</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>229770</t>
+          <t>264902</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>66,78%</t>
+          <t>65,89%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>59,87%</t>
+          <t>59,5%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>73,36%</t>
+          <t>73,07%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>460120</t>
+          <t>488687</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>415612</t>
+          <t>446476</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>499619</t>
+          <t>530946</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>64,52%</t>
+          <t>63,44%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>58,28%</t>
+          <t>57,96%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>70,05%</t>
+          <t>68,93%</t>
         </is>
       </c>
     </row>
@@ -1177,17 +1177,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1212,17 +1212,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6543</t>
+          <t>7896</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2241</t>
+          <t>3511</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>14394</t>
+          <t>17576</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>10739</t>
+          <t>11926</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4308</t>
+          <t>6155</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>18729</t>
+          <t>20623</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>17282</t>
+          <t>19823</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>9691</t>
+          <t>11121</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>28956</t>
+          <t>30726</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,14%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>21687</t>
+          <t>28793</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>13388</t>
+          <t>18250</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>36283</t>
+          <t>44199</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>27040</t>
+          <t>35357</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>15652</t>
+          <t>24977</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>39652</t>
+          <t>50121</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>48728</t>
+          <t>64150</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>33511</t>
+          <t>49105</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>64956</t>
+          <t>83504</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>8,54%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>136916</t>
+          <t>156728</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>112343</t>
+          <t>130402</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>160034</t>
+          <t>183353</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>32,33%</t>
+          <t>32,86%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>26,52%</t>
+          <t>27,34%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>37,78%</t>
+          <t>38,45%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>120230</t>
+          <t>138606</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>75971</t>
+          <t>118232</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>148478</t>
+          <t>160554</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>23,51%</t>
+          <t>27,66%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>23,6%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>29,03%</t>
+          <t>32,04%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>257145</t>
+          <t>295333</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>198874</t>
+          <t>263467</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>295458</t>
+          <t>329286</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>27,5%</t>
+          <t>30,2%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>21,27%</t>
+          <t>26,94%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>31,6%</t>
+          <t>33,67%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>258401</t>
+          <t>283473</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>232378</t>
+          <t>254543</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>284204</t>
+          <t>311632</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>61,01%</t>
+          <t>59,44%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>54,86%</t>
+          <t>53,38%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>67,1%</t>
+          <t>65,35%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>353495</t>
+          <t>315194</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>320481</t>
+          <t>292111</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>410015</t>
+          <t>337537</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>69,11%</t>
+          <t>62,9%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>62,65%</t>
+          <t>58,3%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>80,16%</t>
+          <t>67,36%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>611896</t>
+          <t>598667</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>569802</t>
+          <t>562965</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>688283</t>
+          <t>632631</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>65,44%</t>
+          <t>61,22%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>60,94%</t>
+          <t>57,56%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>73,61%</t>
+          <t>64,69%</t>
         </is>
       </c>
     </row>
@@ -1746,17 +1746,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>15378</t>
+          <t>22123</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>8770</t>
+          <t>14144</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>24956</t>
+          <t>32719</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>11457</t>
+          <t>14134</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>7310</t>
+          <t>8725</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>18372</t>
+          <t>22103</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>26835</t>
+          <t>36258</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>18588</t>
+          <t>25638</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>37485</t>
+          <t>49352</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,98%</t>
         </is>
       </c>
     </row>
@@ -1976,32 +1976,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>43444</t>
+          <t>52142</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>30863</t>
+          <t>39660</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>57279</t>
+          <t>69688</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2011,32 +2011,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>27456</t>
+          <t>33549</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>19101</t>
+          <t>24097</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>35974</t>
+          <t>43812</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2046,32 +2046,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>70900</t>
+          <t>85691</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>55230</t>
+          <t>68882</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>86308</t>
+          <t>104389</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>8,42%</t>
         </is>
       </c>
     </row>
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>150778</t>
+          <t>177767</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>130786</t>
+          <t>155873</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>172985</t>
+          <t>203685</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>28,17%</t>
+          <t>28,69%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>24,43%</t>
+          <t>25,15%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>32,31%</t>
+          <t>32,87%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>168403</t>
+          <t>193848</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>151498</t>
+          <t>174516</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>186930</t>
+          <t>217264</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>31,14%</t>
+          <t>31,25%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>28,01%</t>
+          <t>28,13%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>34,57%</t>
+          <t>35,02%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>319181</t>
+          <t>371615</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>293326</t>
+          <t>340428</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>348839</t>
+          <t>403641</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>29,66%</t>
+          <t>29,97%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>27,26%</t>
+          <t>27,45%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>32,42%</t>
+          <t>32,55%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>325713</t>
+          <t>367649</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>301557</t>
+          <t>339561</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>349408</t>
+          <t>391169</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>60,85%</t>
+          <t>59,33%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>56,33%</t>
+          <t>54,8%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>65,27%</t>
+          <t>63,12%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>333479</t>
+          <t>378843</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>316000</t>
+          <t>355776</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>352944</t>
+          <t>400319</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>61,66%</t>
+          <t>61,07%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>58,43%</t>
+          <t>57,35%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>65,26%</t>
+          <t>64,53%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>659192</t>
+          <t>746492</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>625648</t>
+          <t>714205</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>686096</t>
+          <t>781565</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>61,26%</t>
+          <t>60,2%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>58,14%</t>
+          <t>57,59%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>63,76%</t>
+          <t>63,03%</t>
         </is>
       </c>
     </row>
@@ -2315,17 +2315,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>535313</t>
+          <t>619682</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>535313</t>
+          <t>619682</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>535313</t>
+          <t>619682</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2350,17 +2350,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>540795</t>
+          <t>620374</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>540795</t>
+          <t>620374</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>540795</t>
+          <t>620374</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2385,17 +2385,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1076108</t>
+          <t>1240056</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1076108</t>
+          <t>1240056</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1076108</t>
+          <t>1240056</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2432,32 +2432,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>275539</t>
+          <t>35366</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>37842</t>
+          <t>24883</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>629533</t>
+          <t>49577</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>31,04%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>70,91%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2467,32 +2467,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>20587</t>
+          <t>25998</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>14147</t>
+          <t>18665</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>28748</t>
+          <t>35901</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,32 +2502,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>296126</t>
+          <t>61364</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>56239</t>
+          <t>48093</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>883349</t>
+          <t>77103</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>55,22%</t>
+          <t>5,37%</t>
         </is>
       </c>
     </row>
@@ -2545,32 +2545,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>44474</t>
+          <t>48612</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>19007</t>
+          <t>36670</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>69308</t>
+          <t>65839</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2580,32 +2580,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>40464</t>
+          <t>46771</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>30306</t>
+          <t>37706</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>51743</t>
+          <t>59613</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,32 +2615,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>84938</t>
+          <t>95382</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>49469</t>
+          <t>78418</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>109997</t>
+          <t>114147</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>7,95%</t>
         </is>
       </c>
     </row>
@@ -2658,32 +2658,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>195620</t>
+          <t>208387</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>79302</t>
+          <t>184896</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>282664</t>
+          <t>236088</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>29,74%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>26,39%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>31,84%</t>
+          <t>33,7%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2693,32 +2693,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>236368</t>
+          <t>253312</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>203222</t>
+          <t>232889</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>259740</t>
+          <t>272880</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>33,21%</t>
+          <t>34,43%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>28,55%</t>
+          <t>31,65%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>36,49%</t>
+          <t>37,09%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2728,32 +2728,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>431988</t>
+          <t>461700</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>246035</t>
+          <t>432501</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>523880</t>
+          <t>495553</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>27,01%</t>
+          <t>32,14%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>30,11%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>32,75%</t>
+          <t>34,5%</t>
         </is>
       </c>
     </row>
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>372152</t>
+          <t>408252</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>162136</t>
+          <t>378506</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>528013</t>
+          <t>436257</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>41,92%</t>
+          <t>58,27%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>54,02%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>59,48%</t>
+          <t>62,27%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>414396</t>
+          <t>409710</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>388502</t>
+          <t>388460</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>456925</t>
+          <t>430762</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>58,22%</t>
+          <t>55,68%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>54,58%</t>
+          <t>52,79%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>64,19%</t>
+          <t>58,54%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>786549</t>
+          <t>817962</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>434968</t>
+          <t>782468</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>944860</t>
+          <t>849377</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>49,17%</t>
+          <t>56,94%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>27,19%</t>
+          <t>54,47%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>59,07%</t>
+          <t>59,13%</t>
         </is>
       </c>
     </row>
@@ -2884,17 +2884,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,17 +2919,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>711815</t>
+          <t>735791</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>711815</t>
+          <t>735791</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>711815</t>
+          <t>735791</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1599602</t>
+          <t>1436408</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1599602</t>
+          <t>1436408</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1599602</t>
+          <t>1436408</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -3001,32 +3001,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>33829</t>
+          <t>38714</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>24801</t>
+          <t>27945</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>45899</t>
+          <t>50928</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3036,32 +3036,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>25361</t>
+          <t>29489</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>18535</t>
+          <t>21564</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>33833</t>
+          <t>38180</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3071,32 +3071,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>59190</t>
+          <t>68203</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>47698</t>
+          <t>54345</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>72715</t>
+          <t>84517</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,95%</t>
         </is>
       </c>
     </row>
@@ -3114,32 +3114,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>59574</t>
+          <t>64597</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>47464</t>
+          <t>52400</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>73707</t>
+          <t>79287</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3149,32 +3149,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>55803</t>
+          <t>61906</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>47019</t>
+          <t>50376</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>67974</t>
+          <t>73952</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3184,27 +3184,27 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>115376</t>
+          <t>126503</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>100194</t>
+          <t>109117</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>133136</t>
+          <t>146287</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3227,32 +3227,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>180654</t>
+          <t>197109</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>160614</t>
+          <t>174807</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>202702</t>
+          <t>220057</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>32,19%</t>
+          <t>32,35%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>28,62%</t>
+          <t>28,69%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>36,12%</t>
+          <t>36,11%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3262,32 +3262,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>209975</t>
+          <t>230788</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>192957</t>
+          <t>214043</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>227078</t>
+          <t>250908</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>38,41%</t>
+          <t>37,99%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>35,3%</t>
+          <t>35,23%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>41,54%</t>
+          <t>41,3%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3297,32 +3297,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>390629</t>
+          <t>427897</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>362112</t>
+          <t>399385</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>417899</t>
+          <t>455358</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>35,26%</t>
+          <t>35,16%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>32,68%</t>
+          <t>32,82%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>37,72%</t>
+          <t>37,42%</t>
         </is>
       </c>
     </row>
@@ -3340,32 +3340,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>287178</t>
+          <t>308926</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>265558</t>
+          <t>286151</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>311619</t>
+          <t>331082</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>51,17%</t>
+          <t>50,7%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>47,32%</t>
+          <t>46,96%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>55,52%</t>
+          <t>54,33%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3375,32 +3375,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>255555</t>
+          <t>285331</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>237729</t>
+          <t>264935</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>272902</t>
+          <t>302379</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>46,75%</t>
+          <t>46,97%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>43,48%</t>
+          <t>43,61%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>49,92%</t>
+          <t>49,77%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3410,32 +3410,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>542733</t>
+          <t>594257</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>517610</t>
+          <t>565712</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>573632</t>
+          <t>625711</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>48,99%</t>
+          <t>48,84%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>46,72%</t>
+          <t>46,49%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>51,78%</t>
+          <t>51,42%</t>
         </is>
       </c>
     </row>
@@ -3453,17 +3453,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>546694</t>
+          <t>607514</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>546694</t>
+          <t>607514</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>546694</t>
+          <t>607514</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>1107928</t>
+          <t>1216860</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1107928</t>
+          <t>1216860</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1107928</t>
+          <t>1216860</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3570,32 +3570,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>14311</t>
+          <t>15530</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>8803</t>
+          <t>9923</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>19907</t>
+          <t>23375</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3605,32 +3605,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>21568</t>
+          <t>24598</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>8279</t>
+          <t>17613</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>35582</t>
+          <t>32066</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3640,32 +3640,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>35879</t>
+          <t>40128</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>18546</t>
+          <t>30857</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>50410</t>
+          <t>50429</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,96%</t>
         </is>
       </c>
     </row>
@@ -3683,32 +3683,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>31956</t>
+          <t>34587</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>24473</t>
+          <t>25512</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>41043</t>
+          <t>43759</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3718,32 +3718,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>57627</t>
+          <t>63072</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>26248</t>
+          <t>53049</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>91814</t>
+          <t>73670</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>12,08%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>16,77%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3753,32 +3753,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>89584</t>
+          <t>97659</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>47168</t>
+          <t>83804</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>119622</t>
+          <t>113096</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>13,36%</t>
         </is>
       </c>
     </row>
@@ -3796,32 +3796,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>129668</t>
+          <t>144662</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>115403</t>
+          <t>128232</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>145639</t>
+          <t>161080</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>35,22%</t>
+          <t>35,54%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>31,35%</t>
+          <t>31,5%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>39,56%</t>
+          <t>39,57%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3831,32 +3831,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>154036</t>
+          <t>164656</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>68761</t>
+          <t>150789</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>239337</t>
+          <t>179282</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>25,32%</t>
+          <t>37,49%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>34,34%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>39,34%</t>
+          <t>40,82%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3866,32 +3866,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>283703</t>
+          <t>309317</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>148778</t>
+          <t>287463</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>368950</t>
+          <t>332277</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>29,05%</t>
+          <t>36,55%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>33,97%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>37,78%</t>
+          <t>39,26%</t>
         </is>
       </c>
     </row>
@@ -3909,32 +3909,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>192230</t>
+          <t>212301</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>176393</t>
+          <t>196428</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>207389</t>
+          <t>230090</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>52,21%</t>
+          <t>52,15%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>47,91%</t>
+          <t>48,25%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>56,33%</t>
+          <t>56,52%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3944,32 +3944,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>375137</t>
+          <t>186840</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>249968</t>
+          <t>171410</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>501938</t>
+          <t>201498</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>61,66%</t>
+          <t>42,54%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>41,09%</t>
+          <t>39,03%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>82,51%</t>
+          <t>45,88%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3979,32 +3979,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>567367</t>
+          <t>399142</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>446895</t>
+          <t>378176</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>759689</t>
+          <t>422541</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>58,1%</t>
+          <t>47,17%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>45,76%</t>
+          <t>44,69%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>77,79%</t>
+          <t>49,93%</t>
         </is>
       </c>
     </row>
@@ -4022,17 +4022,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4057,17 +4057,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4092,17 +4092,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4139,17 +4139,17 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>21404</t>
+          <t>23474</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>15241</t>
+          <t>16833</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>28518</t>
+          <t>31556</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4159,12 +4159,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4174,32 +4174,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>44178</t>
+          <t>48866</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>35243</t>
+          <t>38347</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>53522</t>
+          <t>57988</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4209,32 +4209,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>65583</t>
+          <t>72340</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>55650</t>
+          <t>60156</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>78071</t>
+          <t>86701</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>11,23%</t>
         </is>
       </c>
     </row>
@@ -4252,32 +4252,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>31818</t>
+          <t>33889</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>24461</t>
+          <t>26001</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>40058</t>
+          <t>44676</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4287,32 +4287,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>74637</t>
+          <t>80648</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>64293</t>
+          <t>70003</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>85801</t>
+          <t>92714</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>17,43%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>20,04%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4322,32 +4322,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>106455</t>
+          <t>114537</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>92565</t>
+          <t>102632</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>120033</t>
+          <t>130583</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>16,92%</t>
         </is>
       </c>
     </row>
@@ -4365,32 +4365,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>101351</t>
+          <t>113100</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>89620</t>
+          <t>99095</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>114574</t>
+          <t>128796</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>35,95%</t>
+          <t>36,57%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>31,79%</t>
+          <t>32,04%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>40,64%</t>
+          <t>41,64%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4400,32 +4400,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>162242</t>
+          <t>177441</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>148354</t>
+          <t>160484</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>175132</t>
+          <t>192751</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>38,27%</t>
+          <t>38,36%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>34,99%</t>
+          <t>34,69%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>41,31%</t>
+          <t>41,66%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4435,32 +4435,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>263592</t>
+          <t>290541</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>245396</t>
+          <t>269314</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>282640</t>
+          <t>310417</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>37,34%</t>
+          <t>37,64%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>34,77%</t>
+          <t>34,89%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>40,04%</t>
+          <t>40,22%</t>
         </is>
       </c>
     </row>
@@ -4478,32 +4478,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>127319</t>
+          <t>138809</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>114661</t>
+          <t>124541</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>140405</t>
+          <t>153308</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>45,17%</t>
+          <t>44,88%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>40,68%</t>
+          <t>40,27%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>49,81%</t>
+          <t>49,57%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4513,32 +4513,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>142899</t>
+          <t>155665</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>130976</t>
+          <t>139180</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>158353</t>
+          <t>169988</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>33,71%</t>
+          <t>33,65%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>30,89%</t>
+          <t>30,09%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>37,35%</t>
+          <t>36,74%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4548,32 +4548,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>270218</t>
+          <t>294474</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>251494</t>
+          <t>274218</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>290465</t>
+          <t>316315</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>38,28%</t>
+          <t>38,15%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>35,63%</t>
+          <t>35,53%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>41,15%</t>
+          <t>40,98%</t>
         </is>
       </c>
     </row>
@@ -4591,17 +4591,17 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>281892</t>
+          <t>309271</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>281892</t>
+          <t>309271</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>281892</t>
+          <t>309271</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4626,17 +4626,17 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>423956</t>
+          <t>462621</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>423956</t>
+          <t>462621</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>423956</t>
+          <t>462621</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4661,17 +4661,17 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>705847</t>
+          <t>771892</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>705847</t>
+          <t>771892</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>705847</t>
+          <t>771892</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4708,32 +4708,32 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>370173</t>
+          <t>148181</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>126748</t>
+          <t>126418</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>1119406</t>
+          <t>173837</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>32,37%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4743,32 +4743,32 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>138186</t>
+          <t>160551</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>112890</t>
+          <t>141049</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>159945</t>
+          <t>182927</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
+          <t>4,31%</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
           <t>3,78%</t>
         </is>
       </c>
-      <c r="O39" s="2" t="inlineStr">
-        <is>
-          <t>3,09%</t>
-        </is>
-      </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4778,32 +4778,32 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>508360</t>
+          <t>308731</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>263767</t>
+          <t>277260</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>1372465</t>
+          <t>342071</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>4,71%</t>
         </is>
       </c>
     </row>
@@ -4821,32 +4821,32 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>239160</t>
+          <t>268859</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>184640</t>
+          <t>239458</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>273593</t>
+          <t>309049</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4856,32 +4856,32 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>302304</t>
+          <t>344256</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>245828</t>
+          <t>316348</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>337159</t>
+          <t>378300</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4891,32 +4891,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>541464</t>
+          <t>613115</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>470160</t>
+          <t>570572</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>592055</t>
+          <t>658392</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>9,07%</t>
         </is>
       </c>
     </row>
@@ -4934,32 +4934,32 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>1034644</t>
+          <t>1144414</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>818316</t>
+          <t>1084585</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>1133051</t>
+          <t>1212257</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>29,92%</t>
+          <t>32,41%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>23,66%</t>
+          <t>30,72%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>32,77%</t>
+          <t>34,33%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4969,32 +4969,32 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>1131713</t>
+          <t>1253798</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>939586</t>
+          <t>1204006</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>1225748</t>
+          <t>1307051</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>30,95%</t>
+          <t>33,62%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>25,7%</t>
+          <t>32,29%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>33,52%</t>
+          <t>35,05%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5004,32 +5004,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>2166357</t>
+          <t>2398212</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>1867144</t>
+          <t>2320272</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>2325161</t>
+          <t>2478695</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>30,45%</t>
+          <t>33,03%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>26,25%</t>
+          <t>31,96%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>32,68%</t>
+          <t>34,14%</t>
         </is>
       </c>
     </row>
@@ -5047,32 +5047,32 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>1813946</t>
+          <t>1969227</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>1350780</t>
+          <t>1897038</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>1979854</t>
+          <t>2033875</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>52,46%</t>
+          <t>55,77%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>39,06%</t>
+          <t>53,73%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>57,26%</t>
+          <t>57,61%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5082,32 +5082,32 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>2084130</t>
+          <t>1970455</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>1959813</t>
+          <t>1913517</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>2344653</t>
+          <t>2019294</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>57,0%</t>
+          <t>52,84%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>53,6%</t>
+          <t>51,31%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>64,13%</t>
+          <t>54,15%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5117,32 +5117,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>3898076</t>
+          <t>3939682</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>3482742</t>
+          <t>3850363</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>4132562</t>
+          <t>4021284</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>54,79%</t>
+          <t>54,27%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>48,95%</t>
+          <t>53,04%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>58,09%</t>
+          <t>55,39%</t>
         </is>
       </c>
     </row>
@@ -5160,17 +5160,17 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>3457924</t>
+          <t>3530680</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>3457924</t>
+          <t>3530680</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>3457924</t>
+          <t>3530680</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5195,17 +5195,17 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>3656333</t>
+          <t>3729060</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>3656333</t>
+          <t>3729060</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>3656333</t>
+          <t>3729060</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5230,17 +5230,17 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>7114257</t>
+          <t>7259740</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>7114257</t>
+          <t>7259740</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>7114257</t>
+          <t>7259740</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
